--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_C.B. PUERTO SAGUNTO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_C.B. PUERTO SAGUNTO.xlsx
@@ -565,13 +565,13 @@
         <v>24</v>
       </c>
       <c r="D2" t="n">
-        <v>119.1455</v>
+        <v>115.5039</v>
       </c>
       <c r="E2" t="n">
-        <v>94.46809999999999</v>
+        <v>85.47320000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>24.6771</v>
+        <v>30.0306</v>
       </c>
       <c r="G2" t="n">
         <v>51.8948</v>
@@ -610,13 +610,13 @@
         <v>47.647</v>
       </c>
       <c r="S2" t="n">
-        <v>15.833</v>
+        <v>12.1915</v>
       </c>
       <c r="T2" t="n">
-        <v>17.2094</v>
+        <v>8.214399999999999</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.3762</v>
+        <v>3.9772</v>
       </c>
       <c r="V2" t="n">
         <v>37.4899</v>
@@ -643,13 +643,13 @@
         <v>25</v>
       </c>
       <c r="D3" t="n">
-        <v>70.6807</v>
+        <v>69.614</v>
       </c>
       <c r="E3" t="n">
-        <v>42.029</v>
+        <v>42.0861</v>
       </c>
       <c r="F3" t="n">
-        <v>28.6524</v>
+        <v>27.5281</v>
       </c>
       <c r="G3" t="n">
         <v>40.6258</v>
@@ -688,13 +688,13 @@
         <v>46.1806</v>
       </c>
       <c r="S3" t="n">
-        <v>15.5339</v>
+        <v>14.4673</v>
       </c>
       <c r="T3" t="n">
-        <v>8.1806</v>
+        <v>8.238099999999999</v>
       </c>
       <c r="U3" t="n">
-        <v>7.353199999999999</v>
+        <v>6.2293</v>
       </c>
       <c r="V3" t="n">
         <v>15.9871</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S. YURCHENKO</t>
+          <t>A. MONRABAL ROMEU</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D4" t="n">
-        <v>58.9127</v>
+        <v>57.5462</v>
       </c>
       <c r="E4" t="n">
-        <v>35.736</v>
+        <v>41.0146</v>
       </c>
       <c r="F4" t="n">
-        <v>23.1768</v>
+        <v>16.5317</v>
       </c>
       <c r="G4" t="n">
-        <v>23.8536</v>
+        <v>38.5185</v>
       </c>
       <c r="H4" t="n">
-        <v>16.7475</v>
+        <v>7.127000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>7.1061</v>
+        <v>31.3918</v>
       </c>
       <c r="J4" t="n">
-        <v>29.9048</v>
+        <v>52.9967</v>
       </c>
       <c r="K4" t="n">
-        <v>21.6069</v>
+        <v>19.7067</v>
       </c>
       <c r="L4" t="n">
-        <v>8.297700000000001</v>
+        <v>33.29</v>
       </c>
       <c r="M4" t="n">
-        <v>-6.051</v>
+        <v>-14.4784</v>
       </c>
       <c r="N4" t="n">
-        <v>-4.8592</v>
+        <v>-12.5797</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.1918</v>
+        <v>-1.8986</v>
       </c>
       <c r="P4" t="n">
-        <v>8.613099999999999</v>
+        <v>23.0904</v>
       </c>
       <c r="Q4" t="n">
-        <v>-30.4206</v>
+        <v>-23.6404</v>
       </c>
       <c r="R4" t="n">
-        <v>39.0338</v>
+        <v>46.7307</v>
       </c>
       <c r="S4" t="n">
-        <v>28.205</v>
+        <v>10.74</v>
       </c>
       <c r="T4" t="n">
-        <v>21.8684</v>
+        <v>6.891</v>
       </c>
       <c r="U4" t="n">
-        <v>6.3364</v>
+        <v>3.8489</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.759199999999999</v>
+        <v>-14.8028</v>
       </c>
       <c r="W4" t="n">
-        <v>14.3834</v>
+        <v>4.7667</v>
       </c>
       <c r="X4" t="n">
-        <v>-16.1429</v>
+        <v>-19.5695</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. DE LA CAL DOMINGUEZ</t>
+          <t>J. RODENAS SANCHEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D5" t="n">
-        <v>51.1478</v>
+        <v>53.5458</v>
       </c>
       <c r="E5" t="n">
-        <v>19.4663</v>
+        <v>27.6483</v>
       </c>
       <c r="F5" t="n">
-        <v>31.682</v>
+        <v>25.8979</v>
       </c>
       <c r="G5" t="n">
-        <v>27.0277</v>
+        <v>45.2226</v>
       </c>
       <c r="H5" t="n">
-        <v>13.0223</v>
+        <v>22.3013</v>
       </c>
       <c r="I5" t="n">
-        <v>14.0057</v>
+        <v>22.9212</v>
       </c>
       <c r="J5" t="n">
-        <v>38.9386</v>
+        <v>55.62130000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>23.4836</v>
+        <v>33.7827</v>
       </c>
       <c r="L5" t="n">
-        <v>15.4548</v>
+        <v>21.8385</v>
       </c>
       <c r="M5" t="n">
-        <v>-11.9107</v>
+        <v>-10.3985</v>
       </c>
       <c r="N5" t="n">
-        <v>-10.4613</v>
+        <v>-11.4813</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.4496</v>
+        <v>1.0823</v>
       </c>
       <c r="P5" t="n">
-        <v>9.7125</v>
+        <v>-3.1154</v>
       </c>
       <c r="Q5" t="n">
-        <v>-37.0182</v>
+        <v>-53.8779</v>
       </c>
       <c r="R5" t="n">
-        <v>46.7307</v>
+        <v>50.7623</v>
       </c>
       <c r="S5" t="n">
-        <v>13.4579</v>
+        <v>-0.5872000000000002</v>
       </c>
       <c r="T5" t="n">
-        <v>7.285</v>
+        <v>1.1048</v>
       </c>
       <c r="U5" t="n">
-        <v>6.173500000000001</v>
+        <v>-1.692</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9492999999999996</v>
+        <v>12.0259</v>
       </c>
       <c r="W5" t="n">
-        <v>10.2609</v>
+        <v>24.7993</v>
       </c>
       <c r="X5" t="n">
-        <v>-9.311500000000001</v>
+        <v>-12.7737</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. MONRABAL ROMEU</t>
+          <t>A. DE LA CAL DOMINGUEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D6" t="n">
-        <v>46.2318</v>
+        <v>47.7081</v>
       </c>
       <c r="E6" t="n">
-        <v>34.33629999999999</v>
+        <v>17.0094</v>
       </c>
       <c r="F6" t="n">
-        <v>11.8953</v>
+        <v>30.6989</v>
       </c>
       <c r="G6" t="n">
-        <v>38.5185</v>
+        <v>27.0277</v>
       </c>
       <c r="H6" t="n">
-        <v>7.127000000000001</v>
+        <v>13.0223</v>
       </c>
       <c r="I6" t="n">
-        <v>31.3918</v>
+        <v>14.0057</v>
       </c>
       <c r="J6" t="n">
-        <v>52.9967</v>
+        <v>38.9386</v>
       </c>
       <c r="K6" t="n">
-        <v>19.7067</v>
+        <v>23.4836</v>
       </c>
       <c r="L6" t="n">
-        <v>33.29</v>
+        <v>15.4548</v>
       </c>
       <c r="M6" t="n">
-        <v>-14.4784</v>
+        <v>-11.9107</v>
       </c>
       <c r="N6" t="n">
-        <v>-12.5797</v>
+        <v>-10.4613</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.8986</v>
+        <v>-1.4496</v>
       </c>
       <c r="P6" t="n">
-        <v>23.0904</v>
+        <v>9.7125</v>
       </c>
       <c r="Q6" t="n">
-        <v>-23.6404</v>
+        <v>-37.0182</v>
       </c>
       <c r="R6" t="n">
         <v>46.7307</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5743</v>
+        <v>10.0186</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2130999999999999</v>
+        <v>4.8282</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.7873</v>
+        <v>5.1905</v>
       </c>
       <c r="V6" t="n">
-        <v>-14.8028</v>
+        <v>0.9492999999999996</v>
       </c>
       <c r="W6" t="n">
-        <v>4.7667</v>
+        <v>10.2609</v>
       </c>
       <c r="X6" t="n">
-        <v>-19.5695</v>
+        <v>-9.311500000000001</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. MASIP CANTERO</t>
+          <t>S. YURCHENKO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>26</v>
       </c>
       <c r="D7" t="n">
-        <v>39.2201</v>
+        <v>46.7765</v>
       </c>
       <c r="E7" t="n">
-        <v>27.4638</v>
+        <v>25.3397</v>
       </c>
       <c r="F7" t="n">
-        <v>11.7562</v>
+        <v>21.4365</v>
       </c>
       <c r="G7" t="n">
-        <v>28.0265</v>
+        <v>23.8536</v>
       </c>
       <c r="H7" t="n">
-        <v>24.8063</v>
+        <v>16.7475</v>
       </c>
       <c r="I7" t="n">
-        <v>3.2199</v>
+        <v>7.1061</v>
       </c>
       <c r="J7" t="n">
-        <v>40.1344</v>
+        <v>29.9048</v>
       </c>
       <c r="K7" t="n">
-        <v>37.3247</v>
+        <v>21.6069</v>
       </c>
       <c r="L7" t="n">
-        <v>2.8096</v>
+        <v>8.297700000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>-12.1077</v>
+        <v>-6.051</v>
       </c>
       <c r="N7" t="n">
-        <v>-12.5184</v>
+        <v>-4.8592</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4103</v>
+        <v>-1.1918</v>
       </c>
       <c r="P7" t="n">
-        <v>8.063499999999999</v>
+        <v>8.613099999999999</v>
       </c>
       <c r="Q7" t="n">
-        <v>-31.1539</v>
+        <v>-30.4206</v>
       </c>
       <c r="R7" t="n">
-        <v>39.2176</v>
+        <v>39.0338</v>
       </c>
       <c r="S7" t="n">
-        <v>3.9634</v>
+        <v>16.0685</v>
       </c>
       <c r="T7" t="n">
-        <v>0.6415000000000001</v>
+        <v>11.4722</v>
       </c>
       <c r="U7" t="n">
-        <v>3.322</v>
+        <v>4.596500000000001</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.8329000000000004</v>
+        <v>-1.759199999999999</v>
       </c>
       <c r="W7" t="n">
-        <v>17.8414</v>
+        <v>14.3834</v>
       </c>
       <c r="X7" t="n">
-        <v>-18.6747</v>
+        <v>-16.1429</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. GOMEZ CARBONELL</t>
+          <t>D. MASIP CANTERO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D8" t="n">
-        <v>33.526</v>
+        <v>40.239</v>
       </c>
       <c r="E8" t="n">
-        <v>17.8919</v>
+        <v>27.9878</v>
       </c>
       <c r="F8" t="n">
-        <v>15.6344</v>
+        <v>12.2512</v>
       </c>
       <c r="G8" t="n">
-        <v>2.4709</v>
+        <v>28.0265</v>
       </c>
       <c r="H8" t="n">
-        <v>12.8167</v>
+        <v>24.8063</v>
       </c>
       <c r="I8" t="n">
-        <v>-10.3458</v>
+        <v>3.2199</v>
       </c>
       <c r="J8" t="n">
-        <v>12.788</v>
+        <v>40.1344</v>
       </c>
       <c r="K8" t="n">
-        <v>19.4099</v>
+        <v>37.3247</v>
       </c>
       <c r="L8" t="n">
-        <v>-6.6218</v>
+        <v>2.8096</v>
       </c>
       <c r="M8" t="n">
-        <v>-10.3171</v>
+        <v>-12.1077</v>
       </c>
       <c r="N8" t="n">
-        <v>-6.5932</v>
+        <v>-12.5184</v>
       </c>
       <c r="O8" t="n">
-        <v>-3.724</v>
+        <v>0.4103</v>
       </c>
       <c r="P8" t="n">
-        <v>7.1469</v>
+        <v>8.063499999999999</v>
       </c>
       <c r="Q8" t="n">
-        <v>-29.5046</v>
+        <v>-31.1539</v>
       </c>
       <c r="R8" t="n">
-        <v>36.6516</v>
+        <v>39.2176</v>
       </c>
       <c r="S8" t="n">
-        <v>22.631</v>
+        <v>4.9824</v>
       </c>
       <c r="T8" t="n">
-        <v>16.7975</v>
+        <v>1.1655</v>
       </c>
       <c r="U8" t="n">
-        <v>5.8327</v>
+        <v>3.8173</v>
       </c>
       <c r="V8" t="n">
-        <v>1.2774</v>
+        <v>-0.8329000000000004</v>
       </c>
       <c r="W8" t="n">
-        <v>17.8105</v>
+        <v>17.8414</v>
       </c>
       <c r="X8" t="n">
-        <v>-16.5332</v>
+        <v>-18.6747</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. RODENAS SANCHEZ</t>
+          <t>H. GOMEZ GARCIA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D9" t="n">
-        <v>28.0573</v>
+        <v>32.9024</v>
       </c>
       <c r="E9" t="n">
-        <v>10.1044</v>
+        <v>12.6805</v>
       </c>
       <c r="F9" t="n">
-        <v>17.9532</v>
+        <v>20.2218</v>
       </c>
       <c r="G9" t="n">
-        <v>45.2226</v>
+        <v>21.2175</v>
       </c>
       <c r="H9" t="n">
-        <v>22.3013</v>
+        <v>9.597</v>
       </c>
       <c r="I9" t="n">
-        <v>22.9212</v>
+        <v>11.6206</v>
       </c>
       <c r="J9" t="n">
-        <v>55.62130000000001</v>
+        <v>25.5714</v>
       </c>
       <c r="K9" t="n">
-        <v>33.7827</v>
+        <v>14.7791</v>
       </c>
       <c r="L9" t="n">
-        <v>21.8385</v>
+        <v>10.7921</v>
       </c>
       <c r="M9" t="n">
-        <v>-10.3985</v>
+        <v>-4.3537</v>
       </c>
       <c r="N9" t="n">
-        <v>-11.4813</v>
+        <v>-5.182399999999999</v>
       </c>
       <c r="O9" t="n">
-        <v>1.0823</v>
+        <v>0.8285999999999998</v>
       </c>
       <c r="P9" t="n">
-        <v>-3.1154</v>
+        <v>12.2782</v>
       </c>
       <c r="Q9" t="n">
-        <v>-53.8779</v>
+        <v>-21.6246</v>
       </c>
       <c r="R9" t="n">
-        <v>50.7623</v>
+        <v>33.9026</v>
       </c>
       <c r="S9" t="n">
-        <v>-26.0757</v>
+        <v>2.0877</v>
       </c>
       <c r="T9" t="n">
-        <v>-16.439</v>
+        <v>0.7370000000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>-9.636200000000001</v>
+        <v>1.3512</v>
       </c>
       <c r="V9" t="n">
-        <v>12.0259</v>
+        <v>-2.6815</v>
       </c>
       <c r="W9" t="n">
-        <v>24.7993</v>
+        <v>7.9967</v>
       </c>
       <c r="X9" t="n">
-        <v>-12.7737</v>
+        <v>-10.678</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>H. GOMEZ GARCIA</t>
+          <t>J. GOMEZ CARBONELL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,70 +1186,70 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D10" t="n">
-        <v>21.4464</v>
+        <v>24.8461</v>
       </c>
       <c r="E10" t="n">
-        <v>5.082800000000001</v>
+        <v>12.1108</v>
       </c>
       <c r="F10" t="n">
-        <v>16.3635</v>
+        <v>12.7352</v>
       </c>
       <c r="G10" t="n">
-        <v>21.2175</v>
+        <v>2.4709</v>
       </c>
       <c r="H10" t="n">
-        <v>9.597</v>
+        <v>12.8167</v>
       </c>
       <c r="I10" t="n">
-        <v>11.6206</v>
+        <v>-10.3458</v>
       </c>
       <c r="J10" t="n">
-        <v>25.5714</v>
+        <v>12.788</v>
       </c>
       <c r="K10" t="n">
-        <v>14.7791</v>
+        <v>19.4099</v>
       </c>
       <c r="L10" t="n">
-        <v>10.7921</v>
+        <v>-6.6218</v>
       </c>
       <c r="M10" t="n">
-        <v>-4.3537</v>
+        <v>-10.3171</v>
       </c>
       <c r="N10" t="n">
-        <v>-5.182399999999999</v>
+        <v>-6.5932</v>
       </c>
       <c r="O10" t="n">
-        <v>0.8285999999999998</v>
+        <v>-3.724</v>
       </c>
       <c r="P10" t="n">
-        <v>12.2782</v>
+        <v>7.1469</v>
       </c>
       <c r="Q10" t="n">
-        <v>-21.6246</v>
+        <v>-29.5046</v>
       </c>
       <c r="R10" t="n">
-        <v>33.9026</v>
+        <v>36.6516</v>
       </c>
       <c r="S10" t="n">
-        <v>-9.3682</v>
+        <v>13.9506</v>
       </c>
       <c r="T10" t="n">
-        <v>-6.8611</v>
+        <v>11.0168</v>
       </c>
       <c r="U10" t="n">
-        <v>-2.5075</v>
+        <v>2.9339</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.6815</v>
+        <v>1.2774</v>
       </c>
       <c r="W10" t="n">
-        <v>7.9967</v>
+        <v>17.8105</v>
       </c>
       <c r="X10" t="n">
-        <v>-10.678</v>
+        <v>-16.5332</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>15.1453</v>
+        <v>15.8426</v>
       </c>
       <c r="E11" t="n">
-        <v>9.285300000000001</v>
+        <v>9.821099999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>5.8599</v>
+        <v>6.0217</v>
       </c>
       <c r="G11" t="n">
         <v>15.8883</v>
@@ -1312,13 +1312,13 @@
         <v>7.5136</v>
       </c>
       <c r="S11" t="n">
-        <v>1.5398</v>
+        <v>2.2373</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3787</v>
+        <v>0.9143999999999999</v>
       </c>
       <c r="U11" t="n">
-        <v>1.1612</v>
+        <v>1.3229</v>
       </c>
       <c r="V11" t="n">
         <v>-0.6335</v>
@@ -1345,13 +1345,13 @@
         <v>19</v>
       </c>
       <c r="D12" t="n">
-        <v>5.459199999999999</v>
+        <v>11.6363</v>
       </c>
       <c r="E12" t="n">
-        <v>-6.573700000000001</v>
+        <v>-2.314099999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>12.0328</v>
+        <v>13.9502</v>
       </c>
       <c r="G12" t="n">
         <v>11.1974</v>
@@ -1390,13 +1390,13 @@
         <v>23.8233</v>
       </c>
       <c r="S12" t="n">
-        <v>-6.586</v>
+        <v>-0.4087</v>
       </c>
       <c r="T12" t="n">
-        <v>-4.452199999999999</v>
+        <v>-0.1926</v>
       </c>
       <c r="U12" t="n">
-        <v>-2.1333</v>
+        <v>-0.216</v>
       </c>
       <c r="V12" t="n">
         <v>-0.8018000000000001</v>
@@ -1423,13 +1423,13 @@
         <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>4.3738</v>
+        <v>5.3217</v>
       </c>
       <c r="E13" t="n">
-        <v>2.9282</v>
+        <v>3.3268</v>
       </c>
       <c r="F13" t="n">
-        <v>1.4456</v>
+        <v>1.9949</v>
       </c>
       <c r="G13" t="n">
         <v>6.5495</v>
@@ -1468,13 +1468,13 @@
         <v>2.7489</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.3248000000000001</v>
+        <v>0.6232</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.09349999999999997</v>
+        <v>0.3051</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2314</v>
+        <v>0.3181</v>
       </c>
       <c r="V13" t="n">
         <v>-0.9346</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S. HATHOUTI LAHRECH</t>
+          <t>A. SAEZ CUARTERO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,76 +1576,76 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.3792000000000002</v>
+        <v>-0.6436999999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>2.4095</v>
+        <v>-1.5624</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.7887</v>
+        <v>0.9187000000000001</v>
       </c>
       <c r="G15" t="n">
-        <v>0.2646999999999999</v>
+        <v>-1.5504</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.0621</v>
+        <v>-1.015</v>
       </c>
       <c r="I15" t="n">
-        <v>1.3267</v>
+        <v>-0.5354</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.02310000000000001</v>
+        <v>-1.3395</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.3566</v>
+        <v>-0.7402</v>
       </c>
       <c r="L15" t="n">
-        <v>0.3334</v>
+        <v>-0.5994</v>
       </c>
       <c r="M15" t="n">
-        <v>0.2878999999999999</v>
+        <v>-0.2109</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.7056</v>
+        <v>-0.2748</v>
       </c>
       <c r="O15" t="n">
-        <v>0.9933000000000001</v>
+        <v>0.06390000000000001</v>
       </c>
       <c r="P15" t="n">
-        <v>1.2828</v>
+        <v>-0.9162999999999999</v>
       </c>
       <c r="Q15" t="n">
-        <v>-3.6652</v>
+        <v>-1.8326</v>
       </c>
       <c r="R15" t="n">
-        <v>4.948</v>
+        <v>0.9162999999999999</v>
       </c>
       <c r="S15" t="n">
-        <v>1.2617</v>
+        <v>0.124</v>
       </c>
       <c r="T15" t="n">
-        <v>2.5978</v>
+        <v>0.3427</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.3365</v>
+        <v>-0.2187</v>
       </c>
       <c r="V15" t="n">
-        <v>-3.1883</v>
+        <v>1.699</v>
       </c>
       <c r="W15" t="n">
-        <v>3.4998</v>
+        <v>1.267</v>
       </c>
       <c r="X15" t="n">
-        <v>-6.688</v>
+        <v>0.432</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. SAEZ CUARTERO</t>
+          <t>S. HATHOUTI LAHRECH</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,70 +1654,70 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.7017000000000001</v>
+        <v>-0.8205000000000002</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.5213</v>
+        <v>1.0634</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8196</v>
+        <v>-1.884</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.5504</v>
+        <v>0.2646999999999999</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.015</v>
+        <v>-1.0621</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.5354</v>
+        <v>1.3267</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.3395</v>
+        <v>-0.02310000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.7402</v>
+        <v>-0.3566</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.5994</v>
+        <v>0.3334</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.2109</v>
+        <v>0.2878999999999999</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.2748</v>
+        <v>-0.7056</v>
       </c>
       <c r="O16" t="n">
-        <v>0.06390000000000001</v>
+        <v>0.9933000000000001</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.9162999999999999</v>
+        <v>1.2828</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.8326</v>
+        <v>-3.6652</v>
       </c>
       <c r="R16" t="n">
-        <v>0.9162999999999999</v>
+        <v>4.948</v>
       </c>
       <c r="S16" t="n">
-        <v>0.06609999999999999</v>
+        <v>0.8202</v>
       </c>
       <c r="T16" t="n">
-        <v>0.3838</v>
+        <v>1.2518</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3178</v>
+        <v>-0.4316</v>
       </c>
       <c r="V16" t="n">
-        <v>1.699</v>
+        <v>-3.1883</v>
       </c>
       <c r="W16" t="n">
-        <v>1.267</v>
+        <v>3.4998</v>
       </c>
       <c r="X16" t="n">
-        <v>0.432</v>
+        <v>-6.688</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>3</v>
       </c>
       <c r="D17" t="n">
-        <v>-5.9051</v>
+        <v>-5.4563</v>
       </c>
       <c r="E17" t="n">
-        <v>-3.9084</v>
+        <v>-3.7161</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.9967</v>
+        <v>-1.7402</v>
       </c>
       <c r="G17" t="n">
         <v>-0.0252</v>
@@ -1780,13 +1780,13 @@
         <v>1.8327</v>
       </c>
       <c r="S17" t="n">
-        <v>0.01800000000000002</v>
+        <v>0.4669</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.46</v>
+        <v>-0.2677</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4781</v>
+        <v>0.7346</v>
       </c>
       <c r="V17" t="n">
         <v>-2.2327</v>
@@ -1813,13 +1813,13 @@
         <v>15</v>
       </c>
       <c r="D18" t="n">
-        <v>-9.910299999999999</v>
+        <v>-6.492100000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>-14.3993</v>
+        <v>-12.0636</v>
       </c>
       <c r="F18" t="n">
-        <v>4.4889</v>
+        <v>5.5716</v>
       </c>
       <c r="G18" t="n">
         <v>-1.451000000000001</v>
@@ -1858,13 +1858,13 @@
         <v>6.597399999999999</v>
       </c>
       <c r="S18" t="n">
-        <v>-4.6581</v>
+        <v>-1.2398</v>
       </c>
       <c r="T18" t="n">
-        <v>-3.5056</v>
+        <v>-1.1698</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.1527</v>
+        <v>-0.07009999999999997</v>
       </c>
       <c r="V18" t="n">
         <v>-1.2358</v>
@@ -1891,13 +1891,13 @@
         <v>26</v>
       </c>
       <c r="D19" t="n">
-        <v>478.0256000000001</v>
+        <v>509.6453000000001</v>
       </c>
       <c r="E19" t="n">
-        <v>276.3742</v>
+        <v>287.4808</v>
       </c>
       <c r="F19" t="n">
-        <v>201.6523</v>
+        <v>222.1648</v>
       </c>
       <c r="G19" t="n">
         <v>311.3065</v>
@@ -1936,16 +1936,16 @@
         <v>435.2371</v>
       </c>
       <c r="S19" t="n">
-        <v>54.9227</v>
+        <v>86.54249999999999</v>
       </c>
       <c r="T19" t="n">
-        <v>43.74440000000001</v>
+        <v>54.85190000000001</v>
       </c>
       <c r="U19" t="n">
-        <v>11.1782</v>
+        <v>31.692</v>
       </c>
       <c r="V19" t="n">
-        <v>40.3255</v>
+        <v>40.32550000000001</v>
       </c>
       <c r="W19" t="n">
         <v>197.2239</v>
